--- a/docs/VALIDATION_CHECKLIST_2026-10-06.xlsx
+++ b/docs/VALIDATION_CHECKLIST_2026-10-06.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Server Side" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Client Side'!$A$1:$F$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Client Side'!$A$1:$F$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Server Side'!$A$1:$F$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -592,15 +592,15 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF('Client Side'!$D$2:$D$108,"Done")</f>
+        <f>COUNTIF('Client Side'!$D$2:$D$115,"Done")</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>COUNTIF('Client Side'!$D$2:$D$108,"Partial")</f>
+        <f>COUNTIF('Client Side'!$D$2:$D$115,"Partial")</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>COUNTIF('Client Side'!$D$2:$D$108,"To Do")</f>
+        <f>COUNTIF('Client Side'!$D$2:$D$115,"To Do")</f>
         <v/>
       </c>
       <c r="E5" s="4">
@@ -612,7 +612,7 @@
         <v/>
       </c>
       <c r="G5" s="4">
-        <f>COUNTIFS('Client Side'!$E$2:$E$108,"P1",'Client Side'!$D$2:$D$108,"&lt;&gt;Done")</f>
+        <f>COUNTIFS('Client Side'!$E$2:$E$115,"P1",'Client Side'!$D$2:$D$115,"&lt;&gt;Done")</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>minlength=8; change to 15</t>
+          <t>2026-10-07: minlength=15</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Client !@#$%^&amp;* only; server any non-alphanumeric</t>
+          <t>2026-10-07: client now accepts any non-alphanumeric, same as server PASSWORD_POLICY_RE</t>
         </is>
       </c>
     </row>
@@ -1154,15 +1154,19 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: Current Password field, verified via prismAuthentication before changing</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
@@ -1180,15 +1184,19 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: last 5 passwords blocked. prismUserPasswordUpdate checks MEM_USER_PASSWORD_HISTORY (check_only call before Cognito change). Deploy: run lambda-functions/sql/MEM_USER_PASSWORD_HISTORY.sql + deploy lambda</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
@@ -1206,15 +1214,19 @@
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: rejects first name, last name or email local part (3+ chars, case-insensitive)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
@@ -1344,17 +1356,17 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Only minLength(6)</t>
+          <t>2026-10-07: shared PasswordPolicyValidator (same regex as server) on add and edit</t>
         </is>
       </c>
     </row>
@@ -2130,15 +2142,19 @@
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: on submit, case-insensitive match against existing plan names (excluding the plan being edited)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
@@ -2156,15 +2172,19 @@
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: max 100, whitespace-only rejected, trimmed on save</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
@@ -2238,15 +2258,19 @@
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F50" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: dropdown lists only status 0 plans with start &lt;= today &lt;= end</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
@@ -2294,17 +2318,17 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>Any file type uploads</t>
+          <t>2026-10-07: accept + extension check: pdf, doc(x), xls(x), csv, txt, png, jpg/jpeg</t>
         </is>
       </c>
     </row>
@@ -2324,15 +2348,19 @@
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F53" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: rejects empty files and files over 10 MB</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
@@ -2350,17 +2378,17 @@
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>Native confirm()</t>
+          <t>2026-10-07: shared ConfirmDialogComponent replaces native confirm()</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2434,19 @@
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F56" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: new task: datepicker min = today + validator; edit keeps existing date valid</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
@@ -2432,15 +2464,19 @@
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: comment max 500 with counter</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
@@ -2484,15 +2520,19 @@
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F59" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: blocks members already owned by the selected user (uses Care_Coordinator_id added to prismGetUserMemberList - deploy needed for admins)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
@@ -2510,17 +2550,17 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>Optional today</t>
+          <t>2026-10-07: reason now required, whitespace-only rejected, max 500, trimmed</t>
         </is>
       </c>
     </row>
@@ -2566,17 +2606,17 @@
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>Server rejects blank (no-longer-patient only)</t>
+          <t>2026-10-07: NotBlankValidator; Yes now blocked until note valid (was not gated). Unlock dialog now shows the NOTE field (form existed but wasn't rendered); note added to audit log</t>
         </is>
       </c>
     </row>
@@ -2596,15 +2636,19 @@
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: note max 500 (both dialogs)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
@@ -2648,15 +2692,19 @@
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: blocks a second row with the same role + page</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
@@ -2674,15 +2722,19 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: editing own role's active PAGE ACCESS row can't change role, page or status</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
@@ -3154,17 +3206,17 @@
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>Member, Risk, Quality, PCR done; Star Performance missing</t>
+          <t>2026-10-07: Star Performance: requires Measure Name + Statistics + at least one M/D/YYYY date column</t>
         </is>
       </c>
     </row>
@@ -3184,17 +3236,17 @@
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F85" s="15" t="inlineStr">
         <is>
-          <t>Member only</t>
+          <t>2026-10-07: all 5 imports reject files with no data rows (shared validateCsvRows)</t>
         </is>
       </c>
     </row>
@@ -3240,15 +3292,19 @@
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F87" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: max 25 MB and 100,000 rows (MAX_CSV_MB / MAX_CSV_ROWS in utilities/csv-import.ts)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="15" t="n">
@@ -3266,15 +3322,19 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F88" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: required key columns, dates, numbers per file (ROW_RULES). Required columns inferred - confirm with business</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="n">
@@ -3292,17 +3352,17 @@
       </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
         <is>
-          <t>Member file silently skips rows</t>
+          <t>2026-10-07: upload blocked and bad lines listed (line number + reason) via app-csv-errors</t>
         </is>
       </c>
     </row>
@@ -3322,17 +3382,17 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>Member file uses split(','); use Papa Parse</t>
+          <t>2026-10-07: member file now uses Papa Parse like the others</t>
         </is>
       </c>
     </row>
@@ -3352,15 +3412,19 @@
       </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E91" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F91" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: exact duplicate rows reported (star: same measure/statistic/date)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="n">
@@ -3434,17 +3498,17 @@
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>Only server, one Lambda</t>
+          <t>2026-10-07: 366-day max (same as server) on Appointments, Action Log, Outreach, Gaps, System Log</t>
         </is>
       </c>
     </row>
@@ -3464,15 +3528,19 @@
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F95" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: Action Log, Outreach, Gaps, System Log. Appointments allow future (upcoming appointments)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="n">
@@ -3490,15 +3558,19 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F96" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: Star Performance year/plan required, year list now current year - 4. Member Risk has only a user dropdown - nothing to validate</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="n">
@@ -3516,17 +3588,17 @@
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E97" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>CSV injection risk</t>
+          <t>2026-10-07: csvCell() on Appointments, Outreach, Gaps CSV. Pipe-delimited gaps feed unchanged (data format)</t>
         </is>
       </c>
     </row>
@@ -3636,17 +3708,17 @@
       </c>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E101" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F101" s="15" t="inlineStr">
         <is>
-          <t>HeaderService.setTitle runs after load, reads localStorage</t>
+          <t>2026-10-07: authGuard checks page access before the page loads. Still client-side; Lambdas are the real control</t>
         </is>
       </c>
     </row>
@@ -3666,17 +3738,17 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>app.routes.ts has 0 canActivate</t>
+          <t>2026-10-07: authGuard on every app route (login, pending password change, page access); changePasswordGuard</t>
         </is>
       </c>
     </row>
@@ -3696,17 +3768,17 @@
       </c>
       <c r="D103" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E103" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F103" s="15" t="inlineStr">
         <is>
-          <t>calllist-dialog.service.ts bypassSecurityTrustHtml with raw notes</t>
+          <t>2026-10-07: shared escapeHtml on call list (and benefits dates); benefits link only for https URLs</t>
         </is>
       </c>
     </row>
@@ -3726,17 +3798,17 @@
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>environment.ts -&gt; calculateSecretHash</t>
+          <t>2026-10-07: verified - dev uses public app client, no secret/SecretHash in frontend. Prod must also use a public client</t>
         </is>
       </c>
     </row>
@@ -3756,15 +3828,19 @@
       </c>
       <c r="D105" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E105" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F105" s="15" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: interceptor shows a 'no permission' message on 403 when logged in; error still passed to page</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="n">
@@ -3782,17 +3858,17 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>appIntegerOnly / appIntegerPositiveOnly never used</t>
+          <t>2026-10-07: N/A - directives strip leading zeros (breaks OTP). OTP inputs now strip non-digits in onOtpInput</t>
         </is>
       </c>
     </row>
@@ -3812,17 +3888,17 @@
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E107" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>storageEncryption: false; hard-coded key</t>
+          <t>2026-10-07: decided not to enable - key would ship in bundle. Verified only staff profile stored (tokens in memory); removed unused CryptoService with hard-coded key</t>
         </is>
       </c>
     </row>
@@ -3842,22 +3918,232 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>~18 occurrences</t>
+          <t>2026-10-07: removed outside Add Action (error-reporting, file attach, outreach, importers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>Transfer Member</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>CLOSE button must not submit the form</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: CLOSE had no type, so it submitted the form and could run the transfer; now type="button"</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>Assign Plan</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>CLOSE button must not submit the form</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: CLOSE had no type, so it could run the assignment; now type="button"</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>Appointments SEARCH runs once</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: removed duplicate (click) - the form submit already runs applyFilter()</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>Process File (CSV)</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>File picker accepts .csv by extension</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: all 5 importers check the .csv extension (not MIME), accept=.csv, message shown on rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>Process File (CSV)</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>Confirm before PROCESS; warn when error rows exist</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: app confirm dialog before PROCESS on all 5 importers; warns with error row count when &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Gaps Report REMOVE uses app confirm dialog</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: confirmAction() app dialog replaces native confirm()</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>Alternate Address</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>Alternate Address date not in future</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07: NotFutureDateValidator + datepicker [max]=today. (Stray ~star-performance.html not touched)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F108"/>
+  <autoFilter ref="A1:F115"/>
   <conditionalFormatting sqref="A2:F108">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="Done"</formula>
@@ -3869,11 +4155,22 @@
       <formula>$D2="To Do"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A109:F115">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>$D109="Done"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>$D109="Partial"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>$D109="To Do"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="D2:D108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Done,Partial,To Do"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2:E115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P1,P2,P3,-"</formula1>
     </dataValidation>
   </dataValidations>
